--- a/03_Plantilla_Planning.xlsx
+++ b/03_Plantilla_Planning.xlsx
@@ -71,7 +71,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -93,11 +93,44 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,6 +145,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,114 +522,114 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PLANTILLA DEL PLANNING DE GUÀRDIES — Telediagnòstic IDI</t>
+          <t>PLANNING DE GUÀRDIES — Telediagnòstic IDI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Plantilla genèrica: l'app hi posa les dates i crea o treu pestanyes setmanals segons el mes. També podeu fer servir el «Planning buit» de cada mes (carpeta Plantilles mensuals).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Estructura:</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>• Una pestanya per setmana del mes (Setmana 1 fins Setmana 5).</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Estructura</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>• Cada pestanya té 7 columnes (dilluns a diumenge) i 3 franges horàries (8-16, 16-20, 20-08).</t>
+          <t>• Una pestanya per setmana COMPLETA, de dilluns a diumenge (nom: Setmana NN (dd mmm-dd mmm)).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>• Empleneu la fila 1 amb les dates de cada dia de la setmana abans d'omplir el planning.</t>
+          <t>• La setmana pertany al mes del seu dilluns: el planning pot acabar els primers dies del mes següent.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>• Cada pestanya té 7 columnes (dl→dg) i 3 franges: 8-16, 16-20 i 20-08. La data és a la fila 3.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Convencions de nom per cel·la:</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>• Els dies fora del període (si n'hi ha) surten en gris i no s'han d'omplir.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>• "N: Nom" — torn de Neuro fix</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>• "B: Nom" — torn de Body fix</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Convencions per cel·la</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>• "N i B: Nom" — un sol radiòleg cobreix Neuro i Body</t>
+          <t>• "N: Nom" — torn de Neuro fix · "B: Nom" — torn de Body fix</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• "Grup 1: Nom" / "Grup 2: Nom" — torn repartit en dos grups</t>
+          <t>• "N i B: Nom" — un sol radiòleg cobreix Neuro i Body</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• Festius marcats en groc; afegir prefix "FESTIU — Torn dia/nit" al nom</t>
+          <t>• "Grup 1: Nom" / "Grup 2: Nom" — torn repartit en dos grups</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>• Festius: capçalera groga; prefix "FESTIU — Torn dia/nit".</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Notes:</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>• [SUBSTITUIR — …] — torn fix que cal cobrir a mà (vacances, baixa, NO actiu…).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>• Si un dia no necessita una franja (p. ex. dissabte de tarda perquè és part del torn dia 8-20), deixar les cel·les buides o posar "(inclòs torn dia)".</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>• Els fixos del matí (8-16) NO canvien excepte si el professional té V/C; en aquest cas, substituir per l'opció documentada (sovint Bonfill o Sánchez-Montáñez).</t>
+          <t>No canvieu els noms de les pestanyes ni les files de les franges: els fluxos de Microsoft 365</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>• Empleneu només les pestanyes corresponents als dies del mes (algunes setmanes són parcials a l'inici i final).</t>
+          <t>llegeixen el fitxer automàticament (busquen les pestanyes que contenen "Setmana").</t>
         </is>
       </c>
     </row>
@@ -692,7 +728,7 @@
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="n"/>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
@@ -702,7 +738,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
@@ -712,7 +748,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -722,7 +758,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -732,7 +768,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -766,7 +802,7 @@
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
@@ -776,7 +812,7 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -786,7 +822,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -796,7 +832,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -806,7 +842,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -840,7 +876,7 @@
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
@@ -850,7 +886,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -860,7 +896,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -870,7 +906,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -880,7 +916,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
@@ -989,7 +1025,7 @@
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="n"/>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
@@ -999,7 +1035,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
@@ -1009,7 +1045,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -1019,7 +1055,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -1029,7 +1065,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -1063,7 +1099,7 @@
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
@@ -1073,7 +1109,7 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -1083,7 +1119,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -1093,7 +1129,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -1103,7 +1139,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -1137,7 +1173,7 @@
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
@@ -1147,7 +1183,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -1157,7 +1193,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -1167,7 +1203,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -1177,7 +1213,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
@@ -1286,7 +1322,7 @@
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="n"/>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
@@ -1296,7 +1332,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
@@ -1306,7 +1342,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -1316,7 +1352,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -1326,7 +1362,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -1360,7 +1396,7 @@
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
@@ -1370,7 +1406,7 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -1380,7 +1416,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -1390,7 +1426,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -1400,7 +1436,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -1434,7 +1470,7 @@
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
@@ -1444,7 +1480,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -1454,7 +1490,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -1464,7 +1500,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -1474,7 +1510,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
@@ -1583,7 +1619,7 @@
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="n"/>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
@@ -1593,7 +1629,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
@@ -1603,7 +1639,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -1613,7 +1649,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -1623,7 +1659,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -1657,7 +1693,7 @@
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
@@ -1667,7 +1703,7 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -1677,7 +1713,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -1687,7 +1723,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -1697,7 +1733,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -1731,7 +1767,7 @@
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
@@ -1741,7 +1777,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -1751,7 +1787,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -1761,7 +1797,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -1771,7 +1807,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
@@ -1880,7 +1916,7 @@
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="n"/>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
@@ -1890,7 +1926,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
@@ -1900,7 +1936,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -1910,7 +1946,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -1920,7 +1956,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -1954,7 +1990,7 @@
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
@@ -1964,7 +2000,7 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -1974,7 +2010,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -1984,7 +2020,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -1994,7 +2030,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -2028,7 +2064,7 @@
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
@@ -2038,7 +2074,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -2048,7 +2084,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -2058,7 +2094,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -2068,7 +2104,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
